--- a/pages/shp/uploads/27-11-2025 - 29-11-2025.xlsx
+++ b/pages/shp/uploads/27-11-2025 - 29-11-2025.xlsx
@@ -1,34 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 DATA SRI\EKSPORT\Laporan Penjualan\2025\11. NOVEMBER\upload\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="HEADER" r:id="rId3" sheetId="1"/>
-    <sheet name="ENTITAS" r:id="rId4" sheetId="2"/>
-    <sheet name="DOKUMEN" r:id="rId5" sheetId="3"/>
-    <sheet name="PENGANGKUT" r:id="rId6" sheetId="4"/>
-    <sheet name="KEMASAN" r:id="rId7" sheetId="5"/>
-    <sheet name="KONTAINER" r:id="rId8" sheetId="6"/>
-    <sheet name="KOMPONENBIAYA" r:id="rId9" sheetId="7"/>
-    <sheet name="BARANG" r:id="rId10" sheetId="8"/>
-    <sheet name="BARANGTARIF" r:id="rId11" sheetId="9"/>
-    <sheet name="BARANGDOKUMEN" r:id="rId12" sheetId="10"/>
-    <sheet name="BARANGENTITAS" r:id="rId13" sheetId="11"/>
-    <sheet name="BARANGSPEKKHUSUS" r:id="rId14" sheetId="12"/>
-    <sheet name="BARANGVD" r:id="rId15" sheetId="13"/>
-    <sheet name="BAHANBAKU" r:id="rId16" sheetId="14"/>
-    <sheet name="BAHANBAKUTARIF" r:id="rId17" sheetId="15"/>
-    <sheet name="BAHANBAKUDOKUMEN" r:id="rId18" sheetId="16"/>
-    <sheet name="PUNGUTAN" r:id="rId19" sheetId="17"/>
-    <sheet name="JAMINAN" r:id="rId20" sheetId="18"/>
-    <sheet name="BANKDEVISA" r:id="rId21" sheetId="19"/>
-    <sheet name="VERSI" r:id="rId22" sheetId="20"/>
-    <sheet name="RESPON" r:id="rId23" sheetId="21"/>
+    <sheet name="HEADER" sheetId="1" r:id="rId1"/>
+    <sheet name="ENTITAS" sheetId="2" r:id="rId2"/>
+    <sheet name="DOKUMEN" sheetId="3" r:id="rId3"/>
+    <sheet name="PENGANGKUT" sheetId="4" r:id="rId4"/>
+    <sheet name="KEMASAN" sheetId="5" r:id="rId5"/>
+    <sheet name="KONTAINER" sheetId="6" r:id="rId6"/>
+    <sheet name="KOMPONENBIAYA" sheetId="7" r:id="rId7"/>
+    <sheet name="BARANG" sheetId="8" r:id="rId8"/>
+    <sheet name="BARANGTARIF" sheetId="9" r:id="rId9"/>
+    <sheet name="BARANGDOKUMEN" sheetId="10" r:id="rId10"/>
+    <sheet name="BARANGENTITAS" sheetId="11" r:id="rId11"/>
+    <sheet name="BARANGSPEKKHUSUS" sheetId="12" r:id="rId12"/>
+    <sheet name="BARANGVD" sheetId="13" r:id="rId13"/>
+    <sheet name="BAHANBAKU" sheetId="14" r:id="rId14"/>
+    <sheet name="BAHANBAKUTARIF" sheetId="15" r:id="rId15"/>
+    <sheet name="BAHANBAKUDOKUMEN" sheetId="16" r:id="rId16"/>
+    <sheet name="PUNGUTAN" sheetId="17" r:id="rId17"/>
+    <sheet name="JAMINAN" sheetId="18" r:id="rId18"/>
+    <sheet name="BANKDEVISA" sheetId="19" r:id="rId19"/>
+    <sheet name="VERSI" sheetId="20" r:id="rId20"/>
+    <sheet name="RESPON" sheetId="21" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1462,21 +1468,28 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd-MM-yyyy HH:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.00"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.00"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1499,124 +1512,386 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:DC12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="78" max="78" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="79" max="79" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="83" max="83" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="84" max="84" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="85" max="85" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="86" max="86" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="87" max="87" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="88" max="88" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="89" max="89" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="90" max="90" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="91" max="91" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="92" max="92" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="93" max="93" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="94" max="94" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="95" max="95" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="96" max="96" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="97" max="97" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="98" max="98" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="99" max="99" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="100" max="100" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="101" max="101" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="102" max="102" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="103" max="103" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="104" max="104" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="105" max="105" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="106" max="106" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="107" max="107" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="61" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="92" max="93" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="106" max="107" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:107" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1939,7 +2214,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -2003,56 +2278,56 @@
       <c r="BJ2" t="s">
         <v>120</v>
       </c>
-      <c r="BK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP2" t="n">
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
         <v>0.08</v>
       </c>
-      <c r="BQ2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CC2" t="n">
+      <c r="BQ2">
+        <v>1</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>16738</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2">
+        <v>1</v>
+      </c>
+      <c r="CC2">
         <v>0.85</v>
       </c>
-      <c r="CD2" t="n">
-        <v>0.038</v>
+      <c r="CD2">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE2" t="s">
         <v>121</v>
@@ -2081,11 +2356,11 @@
       <c r="CQ2" t="s">
         <v>118</v>
       </c>
-      <c r="CT2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>0.0</v>
+      <c r="CT2">
+        <v>0</v>
+      </c>
+      <c r="CV2">
+        <v>0</v>
       </c>
       <c r="CZ2" t="s">
         <v>126</v>
@@ -2094,7 +2369,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -2170,56 +2445,56 @@
       <c r="BJ3" t="s">
         <v>120</v>
       </c>
-      <c r="BK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP3" t="n">
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
         <v>0.36</v>
       </c>
-      <c r="BQ3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CC3" t="n">
+      <c r="BQ3">
+        <v>2</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>16738</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
+        <v>2</v>
+      </c>
+      <c r="CC3">
         <v>1.7</v>
       </c>
-      <c r="CD3" t="n">
-        <v>0.038</v>
+      <c r="CD3">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE3" t="s">
         <v>121</v>
@@ -2248,11 +2523,11 @@
       <c r="CQ3" t="s">
         <v>118</v>
       </c>
-      <c r="CT3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>0.0</v>
+      <c r="CT3">
+        <v>0</v>
+      </c>
+      <c r="CV3">
+        <v>0</v>
       </c>
       <c r="CZ3" t="s">
         <v>126</v>
@@ -2261,7 +2536,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>135</v>
       </c>
@@ -2325,56 +2600,56 @@
       <c r="BJ4" t="s">
         <v>120</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BK4">
         <v>0.01</v>
       </c>
-      <c r="BL4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO4" t="n">
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
         <v>0.01</v>
       </c>
-      <c r="BP4" t="n">
+      <c r="BP4">
         <v>0.67</v>
       </c>
-      <c r="BQ4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB4" t="n">
+      <c r="BQ4">
+        <v>8</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>16738</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4">
         <v>2.5</v>
       </c>
-      <c r="CC4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>0.038</v>
+      <c r="CC4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="CD4">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE4" t="s">
         <v>121</v>
@@ -2403,11 +2678,11 @@
       <c r="CQ4" t="s">
         <v>130</v>
       </c>
-      <c r="CT4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>0.0</v>
+      <c r="CT4">
+        <v>0</v>
+      </c>
+      <c r="CV4">
+        <v>0</v>
       </c>
       <c r="CZ4" t="s">
         <v>126</v>
@@ -2416,7 +2691,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>138</v>
       </c>
@@ -2480,56 +2755,56 @@
       <c r="BJ5" t="s">
         <v>120</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BK5">
         <v>0.02</v>
       </c>
-      <c r="BL5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO5" t="n">
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
         <v>0.02</v>
       </c>
-      <c r="BP5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU5" t="n">
+      <c r="BP5">
+        <v>2</v>
+      </c>
+      <c r="BQ5">
+        <v>11</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
         <v>13.02</v>
       </c>
-      <c r="BV5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB5" t="n">
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>16738</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5">
         <v>3.5</v>
       </c>
-      <c r="CC5" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0.038</v>
+      <c r="CC5">
+        <v>3</v>
+      </c>
+      <c r="CD5">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE5" t="s">
         <v>121</v>
@@ -2558,11 +2833,11 @@
       <c r="CQ5" t="s">
         <v>118</v>
       </c>
-      <c r="CT5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>0.0</v>
+      <c r="CT5">
+        <v>0</v>
+      </c>
+      <c r="CV5">
+        <v>0</v>
       </c>
       <c r="CZ5" t="s">
         <v>126</v>
@@ -2571,7 +2846,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -2647,56 +2922,56 @@
       <c r="BJ6" t="s">
         <v>120</v>
       </c>
-      <c r="BK6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP6" t="n">
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
         <v>0.17</v>
       </c>
-      <c r="BQ6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CC6" t="n">
+      <c r="BQ6">
+        <v>2</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>16738</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6">
+        <v>2</v>
+      </c>
+      <c r="CC6">
         <v>1.7</v>
       </c>
-      <c r="CD6" t="n">
-        <v>0.038</v>
+      <c r="CD6">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE6" t="s">
         <v>121</v>
@@ -2725,11 +3000,11 @@
       <c r="CQ6" t="s">
         <v>118</v>
       </c>
-      <c r="CT6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>0.0</v>
+      <c r="CT6">
+        <v>0</v>
+      </c>
+      <c r="CV6">
+        <v>0</v>
       </c>
       <c r="CZ6" t="s">
         <v>126</v>
@@ -2738,7 +3013,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>147</v>
       </c>
@@ -2799,56 +3074,56 @@
       <c r="BJ7" t="s">
         <v>120</v>
       </c>
-      <c r="BK7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN7" t="n">
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
         <v>3821.58</v>
       </c>
-      <c r="BO7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>9577.54</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB7" t="n">
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>9577.5400000000009</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>16738</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7">
         <v>414.47</v>
       </c>
-      <c r="CC7" t="n">
+      <c r="CC7">
         <v>383.37</v>
       </c>
-      <c r="CD7" t="n">
-        <v>0.0</v>
+      <c r="CD7">
+        <v>0</v>
       </c>
       <c r="CE7" t="s">
         <v>121</v>
@@ -2877,8 +3152,8 @@
       <c r="CQ7" t="s">
         <v>153</v>
       </c>
-      <c r="CT7" t="n">
-        <v>0.0</v>
+      <c r="CT7">
+        <v>0</v>
       </c>
       <c r="CZ7" t="s">
         <v>126</v>
@@ -2887,7 +3162,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>156</v>
       </c>
@@ -2951,56 +3226,56 @@
       <c r="BJ8" t="s">
         <v>120</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BK8">
         <v>0.01</v>
       </c>
-      <c r="BL8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO8" t="n">
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
         <v>0.01</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BP8">
         <v>0.34</v>
       </c>
-      <c r="BQ8" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>0.038</v>
+      <c r="BQ8">
+        <v>4</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>16738</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="CC8">
+        <v>2</v>
+      </c>
+      <c r="CD8">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE8" t="s">
         <v>121</v>
@@ -3029,11 +3304,11 @@
       <c r="CQ8" t="s">
         <v>153</v>
       </c>
-      <c r="CT8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>0.0</v>
+      <c r="CT8">
+        <v>0</v>
+      </c>
+      <c r="CV8">
+        <v>0</v>
       </c>
       <c r="CZ8" t="s">
         <v>126</v>
@@ -3042,7 +3317,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>158</v>
       </c>
@@ -3106,56 +3381,56 @@
       <c r="BJ9" t="s">
         <v>120</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BK9">
         <v>0.01</v>
       </c>
-      <c r="BL9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO9" t="n">
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
         <v>0.01</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BP9">
         <v>0.73</v>
       </c>
-      <c r="BQ9" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB9" t="n">
+      <c r="BQ9">
+        <v>4</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>16738</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9">
         <v>1.2</v>
       </c>
-      <c r="CC9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.038</v>
+      <c r="CC9">
+        <v>1</v>
+      </c>
+      <c r="CD9">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="CE9" t="s">
         <v>121</v>
@@ -3184,11 +3459,11 @@
       <c r="CQ9" t="s">
         <v>118</v>
       </c>
-      <c r="CT9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0.0</v>
+      <c r="CT9">
+        <v>0</v>
+      </c>
+      <c r="CV9">
+        <v>0</v>
       </c>
       <c r="CZ9" t="s">
         <v>126</v>
@@ -3197,7 +3472,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>162</v>
       </c>
@@ -3258,56 +3533,56 @@
       <c r="BJ10" t="s">
         <v>120</v>
       </c>
-      <c r="BK10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN10" t="n">
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
         <v>2246.34</v>
       </c>
-      <c r="BO10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ10" t="n">
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
         <v>5861.14</v>
       </c>
-      <c r="BR10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>308.432</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>280.932</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>0.0</v>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>16738</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10">
+        <v>308.43200000000002</v>
+      </c>
+      <c r="CC10">
+        <v>280.93200000000002</v>
+      </c>
+      <c r="CD10">
+        <v>0</v>
       </c>
       <c r="CE10" t="s">
         <v>121</v>
@@ -3336,8 +3611,8 @@
       <c r="CQ10" t="s">
         <v>153</v>
       </c>
-      <c r="CT10" t="n">
-        <v>0.0</v>
+      <c r="CT10">
+        <v>0</v>
       </c>
       <c r="CZ10" t="s">
         <v>126</v>
@@ -3346,7 +3621,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>164</v>
       </c>
@@ -3419,56 +3694,56 @@
       <c r="BJ11" t="s">
         <v>120</v>
       </c>
-      <c r="BK11" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BP11" t="n">
+      <c r="BK11">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="BP11">
         <v>114.38</v>
       </c>
-      <c r="BQ11" t="n">
-        <v>1360.0</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB11" t="n">
+      <c r="BQ11">
+        <v>1360</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>16738</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11">
         <v>20.97</v>
       </c>
-      <c r="CC11" t="n">
-        <v>18.31</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>0.0</v>
+      <c r="CC11">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="CD11">
+        <v>0</v>
       </c>
       <c r="CE11" t="s">
         <v>121</v>
@@ -3497,8 +3772,8 @@
       <c r="CQ11" t="s">
         <v>130</v>
       </c>
-      <c r="CT11" t="n">
-        <v>0.0</v>
+      <c r="CT11">
+        <v>0</v>
       </c>
       <c r="CZ11" t="s">
         <v>126</v>
@@ -3507,7 +3782,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>172</v>
       </c>
@@ -3568,56 +3843,56 @@
       <c r="BJ12" t="s">
         <v>120</v>
       </c>
-      <c r="BK12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN12" t="n">
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
         <v>886.14</v>
       </c>
-      <c r="BO12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ12" t="n">
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
         <v>2166.12</v>
       </c>
-      <c r="BR12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB12" t="n">
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>16738</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12">
         <v>101.52</v>
       </c>
-      <c r="CC12" t="n">
+      <c r="CC12">
         <v>91.32</v>
       </c>
-      <c r="CD12" t="n">
-        <v>0.0</v>
+      <c r="CD12">
+        <v>0</v>
       </c>
       <c r="CE12" t="s">
         <v>121</v>
@@ -3646,8 +3921,8 @@
       <c r="CQ12" t="s">
         <v>153</v>
       </c>
-      <c r="CT12" t="n">
-        <v>0.0</v>
+      <c r="CT12">
+        <v>0</v>
       </c>
       <c r="CZ12" t="s">
         <v>126</v>
@@ -3657,30 +3932,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3695,29 +3966,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3729,28 +3996,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3765,32 +4028,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3814,56 +4073,51 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:AO1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3989,50 +4243,46 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4110,32 +4360,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4156,31 +4402,27 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4198,36 +4440,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4260,28 +4498,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4295,11 +4529,11 @@
         <v>427</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -4309,11 +4543,11 @@
         <v>428</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -4323,11 +4557,11 @@
         <v>428</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>135</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -4337,11 +4571,11 @@
         <v>428</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>138</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
@@ -4351,11 +4585,11 @@
         <v>428</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>142</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -4365,11 +4599,11 @@
         <v>428</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -4379,11 +4613,11 @@
         <v>429</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>156</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -4393,11 +4627,11 @@
         <v>428</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>158</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -4407,11 +4641,11 @@
         <v>428</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>162</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
@@ -4421,11 +4655,11 @@
         <v>429</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>164</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
@@ -4435,11 +4669,11 @@
         <v>429</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>172</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -4450,41 +4684,37 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:P63"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="39.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="171.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="171.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4534,7 +4764,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -4554,7 +4784,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -4577,7 +4807,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -4609,7 +4839,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -4629,7 +4859,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -4658,7 +4888,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>104</v>
       </c>
@@ -4669,7 +4899,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>127</v>
       </c>
@@ -4701,7 +4931,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>127</v>
       </c>
@@ -4721,7 +4951,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>127</v>
       </c>
@@ -4750,7 +4980,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>127</v>
       </c>
@@ -4761,7 +4991,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>127</v>
       </c>
@@ -4781,7 +5011,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>127</v>
       </c>
@@ -4804,7 +5034,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>135</v>
       </c>
@@ -4827,7 +5057,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>135</v>
       </c>
@@ -4847,7 +5077,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>135</v>
       </c>
@@ -4876,7 +5106,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>135</v>
       </c>
@@ -4908,7 +5138,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>135</v>
       </c>
@@ -4919,7 +5149,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>135</v>
       </c>
@@ -4939,7 +5169,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>138</v>
       </c>
@@ -4971,7 +5201,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>138</v>
       </c>
@@ -4991,7 +5221,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -5020,7 +5250,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -5031,7 +5261,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>138</v>
       </c>
@@ -5051,7 +5281,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>138</v>
       </c>
@@ -5074,7 +5304,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>142</v>
       </c>
@@ -5106,7 +5336,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>142</v>
       </c>
@@ -5126,7 +5356,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -5155,7 +5385,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -5166,7 +5396,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>142</v>
       </c>
@@ -5186,7 +5416,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>142</v>
       </c>
@@ -5209,7 +5439,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>147</v>
       </c>
@@ -5241,7 +5471,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>147</v>
       </c>
@@ -5270,7 +5500,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>147</v>
       </c>
@@ -5290,7 +5520,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>147</v>
       </c>
@@ -5310,7 +5540,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>147</v>
       </c>
@@ -5333,7 +5563,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>156</v>
       </c>
@@ -5365,7 +5595,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>156</v>
       </c>
@@ -5385,7 +5615,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>156</v>
       </c>
@@ -5414,7 +5644,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>156</v>
       </c>
@@ -5425,7 +5655,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -5448,7 +5678,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>156</v>
       </c>
@@ -5468,7 +5698,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>158</v>
       </c>
@@ -5500,7 +5730,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>158</v>
       </c>
@@ -5520,7 +5750,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>158</v>
       </c>
@@ -5549,7 +5779,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>158</v>
       </c>
@@ -5560,7 +5790,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>158</v>
       </c>
@@ -5580,7 +5810,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>158</v>
       </c>
@@ -5603,7 +5833,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>162</v>
       </c>
@@ -5635,7 +5865,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>162</v>
       </c>
@@ -5664,7 +5894,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>162</v>
       </c>
@@ -5684,7 +5914,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>162</v>
       </c>
@@ -5704,7 +5934,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>162</v>
       </c>
@@ -5727,7 +5957,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>164</v>
       </c>
@@ -5750,7 +5980,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -5779,7 +6009,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>164</v>
       </c>
@@ -5799,7 +6029,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>164</v>
       </c>
@@ -5819,7 +6049,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>164</v>
       </c>
@@ -5851,7 +6081,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>172</v>
       </c>
@@ -5883,7 +6113,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -5912,7 +6142,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>172</v>
       </c>
@@ -5932,7 +6162,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>172</v>
       </c>
@@ -5955,7 +6185,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>172</v>
       </c>
@@ -5976,58 +6206,50 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>448</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6041,7 +6263,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -6055,7 +6277,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>156</v>
       </c>
@@ -6069,7 +6291,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>147</v>
       </c>
@@ -6083,7 +6305,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -6097,7 +6319,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -6111,7 +6333,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>172</v>
       </c>
@@ -6125,7 +6347,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -6139,7 +6361,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>127</v>
       </c>
@@ -6153,7 +6375,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>142</v>
       </c>
@@ -6167,7 +6389,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>164</v>
       </c>
@@ -6181,7 +6403,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>104</v>
       </c>
@@ -6195,7 +6417,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>104</v>
       </c>
@@ -6207,32 +6429,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6255,12 +6473,12 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
-        <v>1.0</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>253</v>
@@ -6272,12 +6490,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
-      <c r="B3" t="n">
-        <v>2.0</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>256</v>
@@ -6289,12 +6507,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="n">
-        <v>3.0</v>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>258</v>
@@ -6306,12 +6524,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>104</v>
       </c>
-      <c r="B5" t="n">
-        <v>4.0</v>
+      <c r="B5">
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>260</v>
@@ -6323,12 +6541,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>127</v>
       </c>
-      <c r="B6" t="n">
-        <v>1.0</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>253</v>
@@ -6340,12 +6558,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>127</v>
       </c>
-      <c r="B7" t="n">
-        <v>2.0</v>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>256</v>
@@ -6357,12 +6575,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>127</v>
       </c>
-      <c r="B8" t="n">
-        <v>3.0</v>
+      <c r="B8">
+        <v>3</v>
       </c>
       <c r="C8" t="s">
         <v>258</v>
@@ -6374,12 +6592,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>127</v>
       </c>
-      <c r="B9" t="n">
-        <v>4.0</v>
+      <c r="B9">
+        <v>4</v>
       </c>
       <c r="C9" t="s">
         <v>260</v>
@@ -6391,12 +6609,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>135</v>
       </c>
-      <c r="B10" t="n">
-        <v>1.0</v>
+      <c r="B10">
+        <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>253</v>
@@ -6408,29 +6626,29 @@
         <v>255</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
-      <c r="B11" t="n">
-        <v>2.0</v>
+      <c r="B11">
+        <v>2</v>
       </c>
       <c r="C11" t="s">
         <v>256</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>264</v>
       </c>
       <c r="E11" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>135</v>
       </c>
-      <c r="B12" t="n">
-        <v>3.0</v>
+      <c r="B12">
+        <v>3</v>
       </c>
       <c r="C12" t="s">
         <v>258</v>
@@ -6442,12 +6660,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>135</v>
       </c>
-      <c r="B13" t="n">
-        <v>4.0</v>
+      <c r="B13">
+        <v>4</v>
       </c>
       <c r="C13" t="s">
         <v>260</v>
@@ -6459,12 +6677,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
-      <c r="B14" t="n">
-        <v>1.0</v>
+      <c r="B14">
+        <v>1</v>
       </c>
       <c r="C14" t="s">
         <v>253</v>
@@ -6476,12 +6694,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>138</v>
       </c>
-      <c r="B15" t="n">
-        <v>2.0</v>
+      <c r="B15">
+        <v>2</v>
       </c>
       <c r="C15" t="s">
         <v>256</v>
@@ -6493,12 +6711,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>138</v>
       </c>
-      <c r="B16" t="n">
-        <v>3.0</v>
+      <c r="B16">
+        <v>3</v>
       </c>
       <c r="C16" t="s">
         <v>258</v>
@@ -6510,12 +6728,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>138</v>
       </c>
-      <c r="B17" t="n">
-        <v>4.0</v>
+      <c r="B17">
+        <v>4</v>
       </c>
       <c r="C17" t="s">
         <v>260</v>
@@ -6527,12 +6745,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>142</v>
       </c>
-      <c r="B18" t="n">
-        <v>1.0</v>
+      <c r="B18">
+        <v>1</v>
       </c>
       <c r="C18" t="s">
         <v>253</v>
@@ -6544,12 +6762,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>142</v>
       </c>
-      <c r="B19" t="n">
-        <v>2.0</v>
+      <c r="B19">
+        <v>2</v>
       </c>
       <c r="C19" t="s">
         <v>256</v>
@@ -6561,12 +6779,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>142</v>
       </c>
-      <c r="B20" t="n">
-        <v>3.0</v>
+      <c r="B20">
+        <v>3</v>
       </c>
       <c r="C20" t="s">
         <v>258</v>
@@ -6578,12 +6796,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>142</v>
       </c>
-      <c r="B21" t="n">
-        <v>4.0</v>
+      <c r="B21">
+        <v>4</v>
       </c>
       <c r="C21" t="s">
         <v>260</v>
@@ -6595,12 +6813,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>147</v>
       </c>
-      <c r="B22" t="n">
-        <v>1.0</v>
+      <c r="B22">
+        <v>1</v>
       </c>
       <c r="C22" t="s">
         <v>253</v>
@@ -6612,12 +6830,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>147</v>
       </c>
-      <c r="B23" t="n">
-        <v>2.0</v>
+      <c r="B23">
+        <v>2</v>
       </c>
       <c r="C23" t="s">
         <v>256</v>
@@ -6629,12 +6847,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>147</v>
       </c>
-      <c r="B24" t="n">
-        <v>3.0</v>
+      <c r="B24">
+        <v>3</v>
       </c>
       <c r="C24" t="s">
         <v>258</v>
@@ -6646,12 +6864,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>147</v>
       </c>
-      <c r="B25" t="n">
-        <v>4.0</v>
+      <c r="B25">
+        <v>4</v>
       </c>
       <c r="C25" t="s">
         <v>200</v>
@@ -6663,12 +6881,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>156</v>
       </c>
-      <c r="B26" t="n">
-        <v>1.0</v>
+      <c r="B26">
+        <v>1</v>
       </c>
       <c r="C26" t="s">
         <v>253</v>
@@ -6680,12 +6898,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>156</v>
       </c>
-      <c r="B27" t="n">
-        <v>2.0</v>
+      <c r="B27">
+        <v>2</v>
       </c>
       <c r="C27" t="s">
         <v>256</v>
@@ -6697,12 +6915,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>156</v>
       </c>
-      <c r="B28" t="n">
-        <v>3.0</v>
+      <c r="B28">
+        <v>3</v>
       </c>
       <c r="C28" t="s">
         <v>258</v>
@@ -6714,12 +6932,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>156</v>
       </c>
-      <c r="B29" t="n">
-        <v>4.0</v>
+      <c r="B29">
+        <v>4</v>
       </c>
       <c r="C29" t="s">
         <v>260</v>
@@ -6731,12 +6949,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>158</v>
       </c>
-      <c r="B30" t="n">
-        <v>1.0</v>
+      <c r="B30">
+        <v>1</v>
       </c>
       <c r="C30" t="s">
         <v>253</v>
@@ -6748,12 +6966,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>158</v>
       </c>
-      <c r="B31" t="n">
-        <v>2.0</v>
+      <c r="B31">
+        <v>2</v>
       </c>
       <c r="C31" t="s">
         <v>256</v>
@@ -6765,12 +6983,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>158</v>
       </c>
-      <c r="B32" t="n">
-        <v>3.0</v>
+      <c r="B32">
+        <v>3</v>
       </c>
       <c r="C32" t="s">
         <v>258</v>
@@ -6782,12 +7000,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>158</v>
       </c>
-      <c r="B33" t="n">
-        <v>4.0</v>
+      <c r="B33">
+        <v>4</v>
       </c>
       <c r="C33" t="s">
         <v>260</v>
@@ -6799,12 +7017,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>162</v>
       </c>
-      <c r="B34" t="n">
-        <v>1.0</v>
+      <c r="B34">
+        <v>1</v>
       </c>
       <c r="C34" t="s">
         <v>253</v>
@@ -6816,12 +7034,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>162</v>
       </c>
-      <c r="B35" t="n">
-        <v>2.0</v>
+      <c r="B35">
+        <v>2</v>
       </c>
       <c r="C35" t="s">
         <v>256</v>
@@ -6833,12 +7051,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>162</v>
       </c>
-      <c r="B36" t="n">
-        <v>3.0</v>
+      <c r="B36">
+        <v>3</v>
       </c>
       <c r="C36" t="s">
         <v>258</v>
@@ -6850,12 +7068,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>162</v>
       </c>
-      <c r="B37" t="n">
-        <v>4.0</v>
+      <c r="B37">
+        <v>4</v>
       </c>
       <c r="C37" t="s">
         <v>200</v>
@@ -6867,12 +7085,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>164</v>
       </c>
-      <c r="B38" t="n">
-        <v>1.0</v>
+      <c r="B38">
+        <v>1</v>
       </c>
       <c r="C38" t="s">
         <v>253</v>
@@ -6884,12 +7102,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>164</v>
       </c>
-      <c r="B39" t="n">
-        <v>2.0</v>
+      <c r="B39">
+        <v>2</v>
       </c>
       <c r="C39" t="s">
         <v>256</v>
@@ -6901,12 +7119,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>164</v>
       </c>
-      <c r="B40" t="n">
-        <v>3.0</v>
+      <c r="B40">
+        <v>3</v>
       </c>
       <c r="C40" t="s">
         <v>258</v>
@@ -6918,12 +7136,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>164</v>
       </c>
-      <c r="B41" t="n">
-        <v>4.0</v>
+      <c r="B41">
+        <v>4</v>
       </c>
       <c r="C41" t="s">
         <v>200</v>
@@ -6935,12 +7153,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>164</v>
       </c>
-      <c r="B42" t="n">
-        <v>5.0</v>
+      <c r="B42">
+        <v>5</v>
       </c>
       <c r="C42" t="s">
         <v>200</v>
@@ -6952,12 +7170,12 @@
         <v>284</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>164</v>
       </c>
-      <c r="B43" t="n">
-        <v>6.0</v>
+      <c r="B43">
+        <v>6</v>
       </c>
       <c r="C43" t="s">
         <v>200</v>
@@ -6969,12 +7187,12 @@
         <v>286</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>164</v>
       </c>
-      <c r="B44" t="n">
-        <v>7.0</v>
+      <c r="B44">
+        <v>7</v>
       </c>
       <c r="C44" t="s">
         <v>200</v>
@@ -6986,12 +7204,12 @@
         <v>288</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>164</v>
       </c>
-      <c r="B45" t="n">
-        <v>8.0</v>
+      <c r="B45">
+        <v>8</v>
       </c>
       <c r="C45" t="s">
         <v>200</v>
@@ -7003,12 +7221,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>164</v>
       </c>
-      <c r="B46" t="n">
-        <v>9.0</v>
+      <c r="B46">
+        <v>9</v>
       </c>
       <c r="C46" t="s">
         <v>260</v>
@@ -7020,12 +7238,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>172</v>
       </c>
-      <c r="B47" t="n">
-        <v>1.0</v>
+      <c r="B47">
+        <v>1</v>
       </c>
       <c r="C47" t="s">
         <v>253</v>
@@ -7037,12 +7255,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>172</v>
       </c>
-      <c r="B48" t="n">
-        <v>2.0</v>
+      <c r="B48">
+        <v>2</v>
       </c>
       <c r="C48" t="s">
         <v>256</v>
@@ -7054,12 +7272,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>172</v>
       </c>
-      <c r="B49" t="n">
-        <v>3.0</v>
+      <c r="B49">
+        <v>3</v>
       </c>
       <c r="C49" t="s">
         <v>258</v>
@@ -7071,12 +7289,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>172</v>
       </c>
-      <c r="B50" t="n">
-        <v>4.0</v>
+      <c r="B50">
+        <v>4</v>
       </c>
       <c r="C50" t="s">
         <v>200</v>
@@ -7089,34 +7307,30 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7145,11 +7359,11 @@
         <v>299</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -7165,11 +7379,11 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -7185,11 +7399,11 @@
         <v>304</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>135</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -7205,11 +7419,11 @@
         <v>307</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>138</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
@@ -7225,11 +7439,11 @@
         <v>304</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>142</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -7245,11 +7459,11 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -7265,11 +7479,11 @@
         <v>310</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>156</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -7285,11 +7499,11 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>158</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -7305,11 +7519,11 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>162</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
@@ -7325,11 +7539,11 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>164</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
@@ -7345,11 +7559,11 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>172</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -7366,30 +7580,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7406,187 +7616,187 @@
         <v>313</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>314</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>314</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>135</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>314</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>138</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>314</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>142</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>314</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>315</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>156</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>314</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>158</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>314</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>162</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>315</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>30</v>
       </c>
       <c r="E10" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>164</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
         <v>315</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>172</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>315</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>13</v>
       </c>
       <c r="E12" t="s">
@@ -7594,31 +7804,27 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7639,40 +7845,34 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7735,86 +7935,81 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:BR12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="158.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="59" max="59" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="68" max="68" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="69" max="69" width="30.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="158.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" customWidth="1"/>
+    <col min="17" max="17" width="20.42578125" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" customWidth="1"/>
+    <col min="20" max="22" width="9.140625" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" customWidth="1"/>
+    <col min="24" max="24" width="12.42578125" customWidth="1"/>
+    <col min="25" max="25" width="17.42578125" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" customWidth="1"/>
+    <col min="30" max="30" width="9.42578125" customWidth="1"/>
+    <col min="31" max="31" width="9.140625" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" customWidth="1"/>
+    <col min="33" max="33" width="9.140625" customWidth="1"/>
+    <col min="34" max="34" width="17.42578125" customWidth="1"/>
+    <col min="35" max="35" width="16.42578125" customWidth="1"/>
+    <col min="36" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="47" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:70" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8026,11 +8221,11 @@
         <v>373</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -8057,56 +8252,56 @@
       <c r="J2" t="s">
         <v>376</v>
       </c>
-      <c r="K2" t="n">
-        <v>5.0</v>
+      <c r="K2">
+        <v>5</v>
       </c>
       <c r="L2" t="s">
         <v>314</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="T2">
         <v>0.85</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="V2">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>16738</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
         <v>0.2</v>
       </c>
-      <c r="AK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.0</v>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
       </c>
       <c r="AS2" t="s">
         <v>377</v>
@@ -8114,8 +8309,8 @@
       <c r="AY2" t="s">
         <v>378</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>0.0</v>
+      <c r="BJ2">
+        <v>0</v>
       </c>
       <c r="BO2" t="s">
         <v>108</v>
@@ -8124,11 +8319,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -8155,56 +8350,56 @@
       <c r="J3" t="s">
         <v>376</v>
       </c>
-      <c r="K3" t="n">
-        <v>4.0</v>
+      <c r="K3">
+        <v>4</v>
       </c>
       <c r="L3" t="s">
         <v>314</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="T3">
         <v>1.7</v>
       </c>
-      <c r="V3" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="V3">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>16738</v>
+      </c>
+      <c r="AC3">
+        <v>2</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
         <v>0.5</v>
       </c>
-      <c r="AK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.0</v>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
       </c>
       <c r="AS3" t="s">
         <v>377</v>
@@ -8212,8 +8407,8 @@
       <c r="AY3" t="s">
         <v>378</v>
       </c>
-      <c r="BJ3" t="n">
-        <v>0.0</v>
+      <c r="BJ3">
+        <v>0</v>
       </c>
       <c r="BO3" t="s">
         <v>108</v>
@@ -8222,11 +8417,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>135</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -8253,56 +8448,56 @@
       <c r="J4" t="s">
         <v>376</v>
       </c>
-      <c r="K4" t="n">
-        <v>8.0</v>
+      <c r="K4">
+        <v>8</v>
       </c>
       <c r="L4" t="s">
         <v>314</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.0</v>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="V4">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>16738</v>
+      </c>
+      <c r="AC4">
+        <v>8</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
       </c>
       <c r="AS4" t="s">
         <v>377</v>
@@ -8310,8 +8505,8 @@
       <c r="AY4" t="s">
         <v>378</v>
       </c>
-      <c r="BJ4" t="n">
-        <v>0.0</v>
+      <c r="BJ4">
+        <v>0</v>
       </c>
       <c r="BO4" t="s">
         <v>108</v>
@@ -8320,11 +8515,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>138</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
@@ -8351,56 +8546,56 @@
       <c r="J5" t="s">
         <v>376</v>
       </c>
-      <c r="K5" t="n">
-        <v>11.0</v>
+      <c r="K5">
+        <v>11</v>
       </c>
       <c r="L5" t="s">
         <v>314</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.0</v>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>16738</v>
+      </c>
+      <c r="AC5">
+        <v>11</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
       </c>
       <c r="AS5" t="s">
         <v>377</v>
@@ -8408,8 +8603,8 @@
       <c r="AY5" t="s">
         <v>378</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>0.0</v>
+      <c r="BJ5">
+        <v>0</v>
       </c>
       <c r="BO5" t="s">
         <v>108</v>
@@ -8418,11 +8613,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>142</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -8449,56 +8644,56 @@
       <c r="J6" t="s">
         <v>376</v>
       </c>
-      <c r="K6" t="n">
-        <v>4.0</v>
+      <c r="K6">
+        <v>4</v>
       </c>
       <c r="L6" t="s">
         <v>314</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="T6">
         <v>1.7</v>
       </c>
-      <c r="V6" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ6" t="n">
+      <c r="V6">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>16738</v>
+      </c>
+      <c r="AC6">
+        <v>2</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
         <v>0.5</v>
       </c>
-      <c r="AK6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.0</v>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
       </c>
       <c r="AS6" t="s">
         <v>377</v>
@@ -8506,8 +8701,8 @@
       <c r="AY6" t="s">
         <v>378</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>0.0</v>
+      <c r="BJ6">
+        <v>0</v>
       </c>
       <c r="BO6" t="s">
         <v>108</v>
@@ -8516,11 +8711,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -8547,53 +8742,53 @@
       <c r="J7" t="s">
         <v>376</v>
       </c>
-      <c r="K7" t="n">
-        <v>4718.0</v>
+      <c r="K7">
+        <v>4718</v>
       </c>
       <c r="L7" t="s">
         <v>315</v>
       </c>
-      <c r="M7" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="M7">
+        <v>35</v>
+      </c>
+      <c r="T7">
         <v>383.37</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9577.54</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.0</v>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>16738</v>
+      </c>
+      <c r="AC7">
+        <v>9577.5400000000009</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
       </c>
       <c r="AS7" t="s">
         <v>377</v>
@@ -8601,8 +8796,8 @@
       <c r="AY7" t="s">
         <v>378</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>0.0</v>
+      <c r="BJ7">
+        <v>0</v>
       </c>
       <c r="BO7" t="s">
         <v>108</v>
@@ -8611,11 +8806,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>156</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -8642,56 +8837,56 @@
       <c r="J8" t="s">
         <v>376</v>
       </c>
-      <c r="K8" t="n">
-        <v>20.0</v>
+      <c r="K8">
+        <v>20</v>
       </c>
       <c r="L8" t="s">
         <v>314</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ8" t="n">
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>16738</v>
+      </c>
+      <c r="AC8">
+        <v>4</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
         <v>0.2</v>
       </c>
-      <c r="AK8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.0</v>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
       </c>
       <c r="AS8" t="s">
         <v>377</v>
@@ -8699,8 +8894,8 @@
       <c r="AY8" t="s">
         <v>378</v>
       </c>
-      <c r="BJ8" t="n">
-        <v>0.0</v>
+      <c r="BJ8">
+        <v>0</v>
       </c>
       <c r="BO8" t="s">
         <v>108</v>
@@ -8709,11 +8904,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>158</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -8740,56 +8935,56 @@
       <c r="J9" t="s">
         <v>376</v>
       </c>
-      <c r="K9" t="n">
-        <v>4.0</v>
+      <c r="K9">
+        <v>4</v>
       </c>
       <c r="L9" t="s">
         <v>314</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.0</v>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>16738</v>
+      </c>
+      <c r="AC9">
+        <v>4</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
       </c>
       <c r="AS9" t="s">
         <v>377</v>
@@ -8797,8 +8992,8 @@
       <c r="AY9" t="s">
         <v>378</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>0.0</v>
+      <c r="BJ9">
+        <v>0</v>
       </c>
       <c r="BO9" t="s">
         <v>108</v>
@@ -8807,11 +9002,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>162</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
@@ -8838,53 +9033,53 @@
       <c r="J10" t="s">
         <v>376</v>
       </c>
-      <c r="K10" t="n">
-        <v>3873.0</v>
+      <c r="K10">
+        <v>3873</v>
       </c>
       <c r="L10" t="s">
         <v>315</v>
       </c>
-      <c r="M10" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>280.932</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="M10">
+        <v>30</v>
+      </c>
+      <c r="T10">
+        <v>280.93200000000002</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>16738</v>
+      </c>
+      <c r="AC10">
         <v>5861.14</v>
       </c>
-      <c r="AF10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.0</v>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>1.5133333333333334</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
       </c>
       <c r="AS10" t="s">
         <v>377</v>
@@ -8892,8 +9087,8 @@
       <c r="AY10" t="s">
         <v>378</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>0.0</v>
+      <c r="BJ10">
+        <v>0</v>
       </c>
       <c r="BO10" t="s">
         <v>108</v>
@@ -8902,11 +9097,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>164</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
@@ -8933,53 +9128,53 @@
       <c r="J11" t="s">
         <v>376</v>
       </c>
-      <c r="K11" t="n">
-        <v>40.0</v>
+      <c r="K11">
+        <v>40</v>
       </c>
       <c r="L11" t="s">
         <v>315</v>
       </c>
-      <c r="M11" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>18.31</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1360.0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.0</v>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="T11">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>16738</v>
+      </c>
+      <c r="AC11">
+        <v>1360</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>34</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
       </c>
       <c r="AS11" t="s">
         <v>377</v>
@@ -8987,8 +9182,8 @@
       <c r="AY11" t="s">
         <v>378</v>
       </c>
-      <c r="BJ11" t="n">
-        <v>0.0</v>
+      <c r="BJ11">
+        <v>0</v>
       </c>
       <c r="BO11" t="s">
         <v>108</v>
@@ -8997,11 +9192,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>172</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -9028,53 +9223,53 @@
       <c r="J12" t="s">
         <v>376</v>
       </c>
-      <c r="K12" t="n">
-        <v>1094.0</v>
+      <c r="K12">
+        <v>1094</v>
       </c>
       <c r="L12" t="s">
         <v>315</v>
       </c>
-      <c r="M12" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="M12">
+        <v>13</v>
+      </c>
+      <c r="T12">
         <v>91.32</v>
       </c>
-      <c r="Z12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>16738.0</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>16738</v>
+      </c>
+      <c r="AC12">
         <v>2166.12</v>
       </c>
-      <c r="AF12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
         <v>1.98</v>
       </c>
-      <c r="AK12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.0</v>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
       </c>
       <c r="AS12" t="s">
         <v>377</v>
@@ -9082,8 +9277,8 @@
       <c r="AY12" t="s">
         <v>378</v>
       </c>
-      <c r="BJ12" t="n">
-        <v>0.0</v>
+      <c r="BJ12">
+        <v>0</v>
       </c>
       <c r="BO12" t="s">
         <v>108</v>
@@ -9093,44 +9288,40 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9190,11 +9381,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>